--- a/planillas/medianeria/Planilla medianeria.xlsx
+++ b/planillas/medianeria/Planilla medianeria.xlsx
@@ -29,7 +29,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Bahnschrift Light Condensed"/>
       <sz val="12"/>
     </font>
   </fonts>
